--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R9fbb479da49e47ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R1701e5fd60394aa2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
         <x:v>审计摘要</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>audit_summary汇总源数据量、有效线程、异常、规则、SLA和自动升级控制量，并检查队列映射、异常隔离及线程与SLA根集合一致性</x:v>
+        <x:v>audit_summary汇总数据截止时间、源数据量、有效线程、异常、规则、SLA和自动升级次数</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="56" customHeight="1">
@@ -474,7 +474,7 @@
         <x:v>运行边界</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
-        <x:v>npm run audit调用真实SQLite CLI；输入数据库和规则文件保持只读，SQL执行未成功时不保留未完成的数据库与报告</x:v>
+        <x:v>npm run audit调用真实SQLite CLI；输入数据库和规则文件保持只读，结果写入output目录</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
@@ -487,7 +487,7 @@
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对点</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
         <x:v>SQLite进程与版本；三份业务输入的读取；递归父链结果；json_each展开；队列映射；unixepoch时间差；五张派生表；四份CSV与审计JSON的跨文件对应</x:v>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R1701e5fd60394aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R0a54299cff02447e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,7 +394,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
-        <x:v>虚构并脱敏的内容申诉工单导出、审计报告合同和队列责任映射</x:v>
+        <x:v>字段已脱敏的内容申诉工单导出、审计报告合同和队列责任映射</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
@@ -487,18 +487,18 @@
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>业务核对点</x:v>
+        <x:v>业务核对</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
-        <x:v>SQLite进程与版本；三份业务输入的读取；递归父链结果；json_each展开；队列映射；unixepoch时间差；五张派生表；四份CSV与审计JSON的跨文件对应</x:v>
+        <x:v>核对三份业务输入、递归父链结果、json_each展开、队列映射、unixepoch时间差、五张派生表，以及四份CSV与审计JSON的跨文件对应</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B18" s="21" t="str">
-        <x:v>SQL缩进、注释数量、CTE与临时表名称、等价索引设计、CSV普通行序、JSON键序、数据库页布局以及不改变业务结果的附加说明</x:v>
+        <x:v>输入数据库和规则文件保持只读，不访问外部工单系统，派生数据库、SQL与报告只写入output目录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
